--- a/data/LM5_LMI_Summary.xlsx
+++ b/data/LM5_LMI_Summary.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dafha\Work Colleague\Mba rida\Event\MAILER\without raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dafha\Work Colleague\OS\Mba rida\Event\MAILER\new begin_stk\without raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF6DA8D4-230A-496C-82D7-B6F9E88AE315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB228ED7-37A0-428D-AF23-8392804E1091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{F673BAF6-C00D-42EA-9313-7CB2BD08351B}"/>
   </bookViews>
   <sheets>
-    <sheet name="By Store" sheetId="4" r:id="rId1"/>
-    <sheet name="By Cat" sheetId="5" r:id="rId2"/>
+    <sheet name="By Cat" sheetId="5" r:id="rId1"/>
+    <sheet name="By Store" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -391,11 +393,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -441,10 +444,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -491,11 +494,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A330CECB-2FBC-4EEA-97BC-52EEAA24B3EB}"/>
     <cellStyle name="Normal 3" xfId="3" xr:uid="{306D26D0-5A54-4950-898A-EDF3634FF0A7}"/>
+    <cellStyle name="Normal 4" xfId="4" xr:uid="{149131AB-6DC7-4CB0-B744-5D748FF8840D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -707,812 +711,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DF96BC-A35D-4BE3-A018-46D51126B0E1}">
-  <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="22.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.7109375" style="1"/>
-    <col min="7" max="7" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.7109375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="32"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="6">
-        <v>29618.102450999999</v>
-      </c>
-      <c r="D4" s="6">
-        <v>26159.871238</v>
-      </c>
-      <c r="E4" s="6">
-        <v>3458.231213</v>
-      </c>
-      <c r="F4" s="7">
-        <v>11.676072829855579</v>
-      </c>
-      <c r="G4" s="6">
-        <v>22023.631440999998</v>
-      </c>
-      <c r="H4" s="7">
-        <v>74.358684785548817</v>
-      </c>
-      <c r="I4" s="7">
-        <v>7594.4710100000002</v>
-      </c>
-      <c r="J4" s="7">
-        <v>25.641315214451176</v>
-      </c>
-      <c r="K4" s="1">
-        <v>650</v>
-      </c>
-      <c r="L4" s="1">
-        <v>580</v>
-      </c>
-      <c r="M4" s="7">
-        <v>89.230769230769241</v>
-      </c>
-      <c r="N4" s="1">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="6">
-        <v>12187.095943</v>
-      </c>
-      <c r="D5" s="6">
-        <v>10568.336154000001</v>
-      </c>
-      <c r="E5" s="6">
-        <v>1618.759789</v>
-      </c>
-      <c r="F5" s="7">
-        <v>13.28257196440453</v>
-      </c>
-      <c r="G5" s="6">
-        <v>7969.7747360000003</v>
-      </c>
-      <c r="H5" s="7">
-        <v>65.395191547479897</v>
-      </c>
-      <c r="I5" s="7">
-        <v>4217.321207</v>
-      </c>
-      <c r="J5" s="7">
-        <v>34.604808452520111</v>
-      </c>
-      <c r="K5" s="1">
-        <v>523</v>
-      </c>
-      <c r="L5" s="1">
-        <v>363</v>
-      </c>
-      <c r="M5" s="7">
-        <v>69.407265774378587</v>
-      </c>
-      <c r="N5" s="1">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="6">
-        <v>14613.818728</v>
-      </c>
-      <c r="D6" s="6">
-        <v>12700.167460000001</v>
-      </c>
-      <c r="E6" s="6">
-        <v>1913.6512680000001</v>
-      </c>
-      <c r="F6" s="7">
-        <v>13.09480638577687</v>
-      </c>
-      <c r="G6" s="6">
-        <v>8890.740894999999</v>
-      </c>
-      <c r="H6" s="7">
-        <v>60.837903223511226</v>
-      </c>
-      <c r="I6" s="7">
-        <v>5723.0778330000003</v>
-      </c>
-      <c r="J6" s="7">
-        <v>39.162096776488767</v>
-      </c>
-      <c r="K6" s="1">
-        <v>609</v>
-      </c>
-      <c r="L6" s="1">
-        <v>483</v>
-      </c>
-      <c r="M6" s="7">
-        <v>79.310344827586206</v>
-      </c>
-      <c r="N6" s="1">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="6">
-        <v>19100.122630999998</v>
-      </c>
-      <c r="D7" s="6">
-        <v>17109.885369</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1990.2372620000001</v>
-      </c>
-      <c r="F7" s="7">
-        <v>10.420023475502681</v>
-      </c>
-      <c r="G7" s="6">
-        <v>15261.397712999998</v>
-      </c>
-      <c r="H7" s="7">
-        <v>79.902092818139039</v>
-      </c>
-      <c r="I7" s="7">
-        <v>3838.7249179999999</v>
-      </c>
-      <c r="J7" s="7">
-        <v>20.097907181860965</v>
-      </c>
-      <c r="K7" s="1">
-        <v>650</v>
-      </c>
-      <c r="L7" s="1">
-        <v>577</v>
-      </c>
-      <c r="M7" s="7">
-        <v>88.769230769230774</v>
-      </c>
-      <c r="N7" s="1">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="6">
-        <v>27870.211994000001</v>
-      </c>
-      <c r="D8" s="6">
-        <v>25593.201395</v>
-      </c>
-      <c r="E8" s="6">
-        <v>2277.0105990000002</v>
-      </c>
-      <c r="F8" s="7">
-        <v>8.1700512342360483</v>
-      </c>
-      <c r="G8" s="6">
-        <v>17222.648756000002</v>
-      </c>
-      <c r="H8" s="7">
-        <v>61.795901515595773</v>
-      </c>
-      <c r="I8" s="7">
-        <v>10647.563238000001</v>
-      </c>
-      <c r="J8" s="7">
-        <v>38.204098484404234</v>
-      </c>
-      <c r="K8" s="1">
-        <v>646</v>
-      </c>
-      <c r="L8" s="1">
-        <v>566</v>
-      </c>
-      <c r="M8" s="7">
-        <v>87.616099071207429</v>
-      </c>
-      <c r="N8" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="6">
-        <v>8969.7860079999991</v>
-      </c>
-      <c r="D9" s="6">
-        <v>7619.3663770000003</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1350.419631</v>
-      </c>
-      <c r="F9" s="7">
-        <v>15.055204547751572</v>
-      </c>
-      <c r="G9" s="6">
-        <v>8159.0706089999994</v>
-      </c>
-      <c r="H9" s="7">
-        <v>90.961708581710468</v>
-      </c>
-      <c r="I9" s="7">
-        <v>810.71539900000005</v>
-      </c>
-      <c r="J9" s="7">
-        <v>9.0382914182895426</v>
-      </c>
-      <c r="K9" s="1">
-        <v>564</v>
-      </c>
-      <c r="L9" s="1">
-        <v>456</v>
-      </c>
-      <c r="M9" s="7">
-        <v>80.851063829787222</v>
-      </c>
-      <c r="N9" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="6">
-        <v>14937.272917</v>
-      </c>
-      <c r="D10" s="6">
-        <v>12981.117806</v>
-      </c>
-      <c r="E10" s="6">
-        <v>1956.155111</v>
-      </c>
-      <c r="F10" s="7">
-        <v>13.09579815451932</v>
-      </c>
-      <c r="G10" s="6">
-        <v>10182.49843</v>
-      </c>
-      <c r="H10" s="7">
-        <v>68.168389816399312</v>
-      </c>
-      <c r="I10" s="7">
-        <v>4754.7744869999997</v>
-      </c>
-      <c r="J10" s="7">
-        <v>31.831610183600688</v>
-      </c>
-      <c r="K10" s="1">
-        <v>623</v>
-      </c>
-      <c r="L10" s="1">
-        <v>524</v>
-      </c>
-      <c r="M10" s="7">
-        <v>84.109149277688601</v>
-      </c>
-      <c r="N10" s="1">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="6">
-        <v>9289.7065930000008</v>
-      </c>
-      <c r="D11" s="6">
-        <v>8098.808282</v>
-      </c>
-      <c r="E11" s="6">
-        <v>1190.8983109999999</v>
-      </c>
-      <c r="F11" s="7">
-        <v>12.819547087712845</v>
-      </c>
-      <c r="G11" s="6">
-        <v>6543.8994060000005</v>
-      </c>
-      <c r="H11" s="7">
-        <v>70.442476740126253</v>
-      </c>
-      <c r="I11" s="7">
-        <v>2745.8071869999999</v>
-      </c>
-      <c r="J11" s="7">
-        <v>29.55752325987374</v>
-      </c>
-      <c r="K11" s="1">
-        <v>603</v>
-      </c>
-      <c r="L11" s="1">
-        <v>449</v>
-      </c>
-      <c r="M11" s="7">
-        <v>74.461028192371487</v>
-      </c>
-      <c r="N11" s="1">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="6">
-        <v>7755.6741590000001</v>
-      </c>
-      <c r="D12" s="6">
-        <v>6408.1013279999997</v>
-      </c>
-      <c r="E12" s="6">
-        <v>1347.572831</v>
-      </c>
-      <c r="F12" s="7">
-        <v>17.375315199855599</v>
-      </c>
-      <c r="G12" s="6">
-        <v>6220.4926660000001</v>
-      </c>
-      <c r="H12" s="7">
-        <v>80.205698930524136</v>
-      </c>
-      <c r="I12" s="7">
-        <v>1535.181493</v>
-      </c>
-      <c r="J12" s="7">
-        <v>19.794301069475861</v>
-      </c>
-      <c r="K12" s="1">
-        <v>544</v>
-      </c>
-      <c r="L12" s="1">
-        <v>428</v>
-      </c>
-      <c r="M12" s="7">
-        <v>78.67647058823529</v>
-      </c>
-      <c r="N12" s="1">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="6">
-        <v>7918.950527</v>
-      </c>
-      <c r="D13" s="6">
-        <v>6614.2105519999996</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1304.739975</v>
-      </c>
-      <c r="F13" s="7">
-        <v>16.476172828096768</v>
-      </c>
-      <c r="G13" s="6">
-        <v>6799.3666800000001</v>
-      </c>
-      <c r="H13" s="7">
-        <v>85.861966895957593</v>
-      </c>
-      <c r="I13" s="7">
-        <v>1119.5838470000001</v>
-      </c>
-      <c r="J13" s="7">
-        <v>14.1380331040424</v>
-      </c>
-      <c r="K13" s="1">
-        <v>554</v>
-      </c>
-      <c r="L13" s="1">
-        <v>466</v>
-      </c>
-      <c r="M13" s="7">
-        <v>84.115523465703973</v>
-      </c>
-      <c r="N13" s="1">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="6">
-        <v>6864.213463</v>
-      </c>
-      <c r="D14" s="6">
-        <v>5591.5507189999998</v>
-      </c>
-      <c r="E14" s="6">
-        <v>1272.662744</v>
-      </c>
-      <c r="F14" s="7">
-        <v>18.54054730174116</v>
-      </c>
-      <c r="G14" s="6">
-        <v>5701.9791310000001</v>
-      </c>
-      <c r="H14" s="7">
-        <v>83.068208203827538</v>
-      </c>
-      <c r="I14" s="7">
-        <v>1162.234332</v>
-      </c>
-      <c r="J14" s="7">
-        <v>16.931791796172465</v>
-      </c>
-      <c r="K14" s="1">
-        <v>584</v>
-      </c>
-      <c r="L14" s="1">
-        <v>481</v>
-      </c>
-      <c r="M14" s="7">
-        <v>82.363013698630141</v>
-      </c>
-      <c r="N14" s="1">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="6">
-        <v>12284.520479999999</v>
-      </c>
-      <c r="D15" s="6">
-        <v>10496.985538999999</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1787.5349409999999</v>
-      </c>
-      <c r="F15" s="7">
-        <v>14.551116943556922</v>
-      </c>
-      <c r="G15" s="6">
-        <v>12284.390257999999</v>
-      </c>
-      <c r="H15" s="7">
-        <v>99.998939950483106</v>
-      </c>
-      <c r="I15" s="7">
-        <v>0.130222</v>
-      </c>
-      <c r="J15" s="7">
-        <v>1.060049516885986E-3</v>
-      </c>
-      <c r="K15" s="1">
-        <v>625</v>
-      </c>
-      <c r="L15" s="1">
-        <v>532</v>
-      </c>
-      <c r="M15" s="7">
-        <v>85.11999999999999</v>
-      </c>
-      <c r="N15" s="1">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="6">
-        <v>340.93070999999998</v>
-      </c>
-      <c r="D16" s="6">
-        <v>340.93070999999998</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0</v>
-      </c>
-      <c r="F16" s="7">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6">
-        <v>340.93070999999998</v>
-      </c>
-      <c r="H16" s="7">
-        <v>100</v>
-      </c>
-      <c r="I16" s="7">
-        <v>0</v>
-      </c>
-      <c r="J16" s="7">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-      <c r="L16" s="1">
-        <v>0</v>
-      </c>
-      <c r="M16" s="7">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="6">
-        <v>84.101866999999999</v>
-      </c>
-      <c r="D17" s="6">
-        <v>84.101866999999999</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0</v>
-      </c>
-      <c r="F17" s="7">
-        <v>0</v>
-      </c>
-      <c r="G17" s="6">
-        <v>84.101866999999999</v>
-      </c>
-      <c r="H17" s="7">
-        <v>100</v>
-      </c>
-      <c r="I17" s="7">
-        <v>0</v>
-      </c>
-      <c r="J17" s="7">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <v>2</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-      <c r="M17" s="7">
-        <v>0</v>
-      </c>
-      <c r="N17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="6">
-        <v>0</v>
-      </c>
-      <c r="D18" s="6">
-        <v>0</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0</v>
-      </c>
-      <c r="F18" s="7">
-        <v>0</v>
-      </c>
-      <c r="G18" s="6">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7">
-        <v>0</v>
-      </c>
-      <c r="I18" s="7">
-        <v>0</v>
-      </c>
-      <c r="J18" s="7">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
-        <v>1</v>
-      </c>
-      <c r="L18" s="1">
-        <v>0</v>
-      </c>
-      <c r="M18" s="7">
-        <v>0</v>
-      </c>
-      <c r="N18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="10">
-        <v>171834.50847099995</v>
-      </c>
-      <c r="D19" s="10">
-        <v>150366.63479599994</v>
-      </c>
-      <c r="E19" s="10">
-        <v>21467.873675000003</v>
-      </c>
-      <c r="F19" s="11">
-        <v>12.49334249914247</v>
-      </c>
-      <c r="G19" s="10">
-        <v>127684.92329799999</v>
-      </c>
-      <c r="H19" s="11">
-        <v>74.306915667960283</v>
-      </c>
-      <c r="I19" s="10">
-        <v>44149.585172999999</v>
-      </c>
-      <c r="J19" s="11">
-        <v>25.693084332039746</v>
-      </c>
-      <c r="K19" s="10">
-        <v>7178</v>
-      </c>
-      <c r="L19" s="10">
-        <v>5905</v>
-      </c>
-      <c r="M19" s="11">
-        <v>82.265254945667323</v>
-      </c>
-      <c r="N19" s="10">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C21" s="12"/>
-      <c r="G21" s="12"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:B3"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="K2:N2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8BB6466-52F9-4140-A7C2-5D43EE929BAE}">
   <dimension ref="A1:N36"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -1569,28 +767,28 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="33"/>
       <c r="B3" s="33"/>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="17" t="s">
         <v>40</v>
       </c>
       <c r="K3" s="5" t="s">
@@ -3057,6 +2255,812 @@
       <c r="N36" s="30">
         <v>456</v>
       </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:B3"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="K2:N2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DF96BC-A35D-4BE3-A018-46D51126B0E1}">
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="22.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.7109375" style="1"/>
+    <col min="7" max="7" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.7109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="6">
+        <v>29618.102450999999</v>
+      </c>
+      <c r="D4" s="6">
+        <v>26159.871238</v>
+      </c>
+      <c r="E4" s="6">
+        <v>3458.231213</v>
+      </c>
+      <c r="F4" s="7">
+        <v>11.676072829855579</v>
+      </c>
+      <c r="G4" s="6">
+        <v>22023.631440999998</v>
+      </c>
+      <c r="H4" s="7">
+        <v>74.358684785548817</v>
+      </c>
+      <c r="I4" s="7">
+        <v>7594.4710100000002</v>
+      </c>
+      <c r="J4" s="7">
+        <v>25.641315214451176</v>
+      </c>
+      <c r="K4" s="1">
+        <v>650</v>
+      </c>
+      <c r="L4" s="1">
+        <v>580</v>
+      </c>
+      <c r="M4" s="7">
+        <v>89.230769230769241</v>
+      </c>
+      <c r="N4" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="6">
+        <v>12187.095943</v>
+      </c>
+      <c r="D5" s="6">
+        <v>10568.336154000001</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1618.759789</v>
+      </c>
+      <c r="F5" s="7">
+        <v>13.28257196440453</v>
+      </c>
+      <c r="G5" s="6">
+        <v>7969.7747360000003</v>
+      </c>
+      <c r="H5" s="7">
+        <v>65.395191547479897</v>
+      </c>
+      <c r="I5" s="7">
+        <v>4217.321207</v>
+      </c>
+      <c r="J5" s="7">
+        <v>34.604808452520111</v>
+      </c>
+      <c r="K5" s="1">
+        <v>523</v>
+      </c>
+      <c r="L5" s="1">
+        <v>363</v>
+      </c>
+      <c r="M5" s="7">
+        <v>69.407265774378587</v>
+      </c>
+      <c r="N5" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="6">
+        <v>14613.818728</v>
+      </c>
+      <c r="D6" s="6">
+        <v>12700.167460000001</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1913.6512680000001</v>
+      </c>
+      <c r="F6" s="7">
+        <v>13.09480638577687</v>
+      </c>
+      <c r="G6" s="6">
+        <v>8890.740894999999</v>
+      </c>
+      <c r="H6" s="7">
+        <v>60.837903223511226</v>
+      </c>
+      <c r="I6" s="7">
+        <v>5723.0778330000003</v>
+      </c>
+      <c r="J6" s="7">
+        <v>39.162096776488767</v>
+      </c>
+      <c r="K6" s="1">
+        <v>609</v>
+      </c>
+      <c r="L6" s="1">
+        <v>483</v>
+      </c>
+      <c r="M6" s="7">
+        <v>79.310344827586206</v>
+      </c>
+      <c r="N6" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="6">
+        <v>19100.122630999998</v>
+      </c>
+      <c r="D7" s="6">
+        <v>17109.885369</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1990.2372620000001</v>
+      </c>
+      <c r="F7" s="7">
+        <v>10.420023475502681</v>
+      </c>
+      <c r="G7" s="6">
+        <v>15261.397712999998</v>
+      </c>
+      <c r="H7" s="7">
+        <v>79.902092818139039</v>
+      </c>
+      <c r="I7" s="7">
+        <v>3838.7249179999999</v>
+      </c>
+      <c r="J7" s="7">
+        <v>20.097907181860965</v>
+      </c>
+      <c r="K7" s="1">
+        <v>650</v>
+      </c>
+      <c r="L7" s="1">
+        <v>577</v>
+      </c>
+      <c r="M7" s="7">
+        <v>88.769230769230774</v>
+      </c>
+      <c r="N7" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="6">
+        <v>27870.211994000001</v>
+      </c>
+      <c r="D8" s="6">
+        <v>25593.201395</v>
+      </c>
+      <c r="E8" s="6">
+        <v>2277.0105990000002</v>
+      </c>
+      <c r="F8" s="7">
+        <v>8.1700512342360483</v>
+      </c>
+      <c r="G8" s="6">
+        <v>17222.648756000002</v>
+      </c>
+      <c r="H8" s="7">
+        <v>61.795901515595773</v>
+      </c>
+      <c r="I8" s="7">
+        <v>10647.563238000001</v>
+      </c>
+      <c r="J8" s="7">
+        <v>38.204098484404234</v>
+      </c>
+      <c r="K8" s="1">
+        <v>646</v>
+      </c>
+      <c r="L8" s="1">
+        <v>566</v>
+      </c>
+      <c r="M8" s="7">
+        <v>87.616099071207429</v>
+      </c>
+      <c r="N8" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="6">
+        <v>8969.7860079999991</v>
+      </c>
+      <c r="D9" s="6">
+        <v>7619.3663770000003</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1350.419631</v>
+      </c>
+      <c r="F9" s="7">
+        <v>15.055204547751572</v>
+      </c>
+      <c r="G9" s="6">
+        <v>8159.0706089999994</v>
+      </c>
+      <c r="H9" s="7">
+        <v>90.961708581710468</v>
+      </c>
+      <c r="I9" s="7">
+        <v>810.71539900000005</v>
+      </c>
+      <c r="J9" s="7">
+        <v>9.0382914182895426</v>
+      </c>
+      <c r="K9" s="1">
+        <v>564</v>
+      </c>
+      <c r="L9" s="1">
+        <v>456</v>
+      </c>
+      <c r="M9" s="7">
+        <v>80.851063829787222</v>
+      </c>
+      <c r="N9" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="6">
+        <v>14937.272917</v>
+      </c>
+      <c r="D10" s="6">
+        <v>12981.117806</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1956.155111</v>
+      </c>
+      <c r="F10" s="7">
+        <v>13.09579815451932</v>
+      </c>
+      <c r="G10" s="6">
+        <v>10182.49843</v>
+      </c>
+      <c r="H10" s="7">
+        <v>68.168389816399312</v>
+      </c>
+      <c r="I10" s="7">
+        <v>4754.7744869999997</v>
+      </c>
+      <c r="J10" s="7">
+        <v>31.831610183600688</v>
+      </c>
+      <c r="K10" s="1">
+        <v>623</v>
+      </c>
+      <c r="L10" s="1">
+        <v>524</v>
+      </c>
+      <c r="M10" s="7">
+        <v>84.109149277688601</v>
+      </c>
+      <c r="N10" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="6">
+        <v>9289.7065930000008</v>
+      </c>
+      <c r="D11" s="6">
+        <v>8098.808282</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1190.8983109999999</v>
+      </c>
+      <c r="F11" s="7">
+        <v>12.819547087712845</v>
+      </c>
+      <c r="G11" s="6">
+        <v>6543.8994060000005</v>
+      </c>
+      <c r="H11" s="7">
+        <v>70.442476740126253</v>
+      </c>
+      <c r="I11" s="7">
+        <v>2745.8071869999999</v>
+      </c>
+      <c r="J11" s="7">
+        <v>29.55752325987374</v>
+      </c>
+      <c r="K11" s="1">
+        <v>603</v>
+      </c>
+      <c r="L11" s="1">
+        <v>449</v>
+      </c>
+      <c r="M11" s="7">
+        <v>74.461028192371487</v>
+      </c>
+      <c r="N11" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="6">
+        <v>7755.6741590000001</v>
+      </c>
+      <c r="D12" s="6">
+        <v>6408.1013279999997</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1347.572831</v>
+      </c>
+      <c r="F12" s="7">
+        <v>17.375315199855599</v>
+      </c>
+      <c r="G12" s="6">
+        <v>6220.4926660000001</v>
+      </c>
+      <c r="H12" s="7">
+        <v>80.205698930524136</v>
+      </c>
+      <c r="I12" s="7">
+        <v>1535.181493</v>
+      </c>
+      <c r="J12" s="7">
+        <v>19.794301069475861</v>
+      </c>
+      <c r="K12" s="1">
+        <v>544</v>
+      </c>
+      <c r="L12" s="1">
+        <v>428</v>
+      </c>
+      <c r="M12" s="7">
+        <v>78.67647058823529</v>
+      </c>
+      <c r="N12" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="6">
+        <v>7918.950527</v>
+      </c>
+      <c r="D13" s="6">
+        <v>6614.2105519999996</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1304.739975</v>
+      </c>
+      <c r="F13" s="7">
+        <v>16.476172828096768</v>
+      </c>
+      <c r="G13" s="6">
+        <v>6799.3666800000001</v>
+      </c>
+      <c r="H13" s="7">
+        <v>85.861966895957593</v>
+      </c>
+      <c r="I13" s="7">
+        <v>1119.5838470000001</v>
+      </c>
+      <c r="J13" s="7">
+        <v>14.1380331040424</v>
+      </c>
+      <c r="K13" s="1">
+        <v>554</v>
+      </c>
+      <c r="L13" s="1">
+        <v>466</v>
+      </c>
+      <c r="M13" s="7">
+        <v>84.115523465703973</v>
+      </c>
+      <c r="N13" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="6">
+        <v>6864.213463</v>
+      </c>
+      <c r="D14" s="6">
+        <v>5591.5507189999998</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1272.662744</v>
+      </c>
+      <c r="F14" s="7">
+        <v>18.54054730174116</v>
+      </c>
+      <c r="G14" s="6">
+        <v>5701.9791310000001</v>
+      </c>
+      <c r="H14" s="7">
+        <v>83.068208203827538</v>
+      </c>
+      <c r="I14" s="7">
+        <v>1162.234332</v>
+      </c>
+      <c r="J14" s="7">
+        <v>16.931791796172465</v>
+      </c>
+      <c r="K14" s="1">
+        <v>584</v>
+      </c>
+      <c r="L14" s="1">
+        <v>481</v>
+      </c>
+      <c r="M14" s="7">
+        <v>82.363013698630141</v>
+      </c>
+      <c r="N14" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="6">
+        <v>12284.520479999999</v>
+      </c>
+      <c r="D15" s="6">
+        <v>10496.985538999999</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1787.5349409999999</v>
+      </c>
+      <c r="F15" s="7">
+        <v>14.551116943556922</v>
+      </c>
+      <c r="G15" s="6">
+        <v>12284.390257999999</v>
+      </c>
+      <c r="H15" s="7">
+        <v>99.998939950483106</v>
+      </c>
+      <c r="I15" s="7">
+        <v>0.130222</v>
+      </c>
+      <c r="J15" s="7">
+        <v>1.060049516885986E-3</v>
+      </c>
+      <c r="K15" s="1">
+        <v>625</v>
+      </c>
+      <c r="L15" s="1">
+        <v>532</v>
+      </c>
+      <c r="M15" s="7">
+        <v>85.11999999999999</v>
+      </c>
+      <c r="N15" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="6">
+        <v>340.93070999999998</v>
+      </c>
+      <c r="D16" s="6">
+        <v>340.93070999999998</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6">
+        <v>340.93070999999998</v>
+      </c>
+      <c r="H16" s="7">
+        <v>100</v>
+      </c>
+      <c r="I16" s="7">
+        <v>0</v>
+      </c>
+      <c r="J16" s="7">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="6">
+        <v>84.101866999999999</v>
+      </c>
+      <c r="D17" s="6">
+        <v>84.101866999999999</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6">
+        <v>84.101866999999999</v>
+      </c>
+      <c r="H17" s="7">
+        <v>100</v>
+      </c>
+      <c r="I17" s="7">
+        <v>0</v>
+      </c>
+      <c r="J17" s="7">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>2</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="6">
+        <v>0</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0</v>
+      </c>
+      <c r="I18" s="7">
+        <v>0</v>
+      </c>
+      <c r="J18" s="7">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="7">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="10">
+        <v>171834.50847099995</v>
+      </c>
+      <c r="D19" s="10">
+        <v>150366.63479599994</v>
+      </c>
+      <c r="E19" s="10">
+        <v>21467.873675000003</v>
+      </c>
+      <c r="F19" s="11">
+        <v>12.49334249914247</v>
+      </c>
+      <c r="G19" s="10">
+        <v>127684.92329799999</v>
+      </c>
+      <c r="H19" s="11">
+        <v>74.306915667960283</v>
+      </c>
+      <c r="I19" s="10">
+        <v>44149.585172999999</v>
+      </c>
+      <c r="J19" s="11">
+        <v>25.693084332039746</v>
+      </c>
+      <c r="K19" s="10">
+        <v>7178</v>
+      </c>
+      <c r="L19" s="10">
+        <v>5905</v>
+      </c>
+      <c r="M19" s="11">
+        <v>82.265254945667323</v>
+      </c>
+      <c r="N19" s="10">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C21" s="12"/>
+      <c r="G21" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="4">
